--- a/tools/importer/reports/import-learn-about-medicare.report.xlsx
+++ b/tools/importer/reports/import-learn-about-medicare.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="377">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>employer.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","cards-minimal-dark-withimg-icons","columns-minimal-dark","columns-minimal-dark","columns-minimal-dark"]</t>
+  </si>
+  <si>
+    <t>employer</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>employer-landing</t>
+  </si>
+  <si>
+    <t>2026-09-30T17:19:21.302Z</t>
+  </si>
+  <si>
+    <t>Boost Employee Health and Save Money with Highmark Employer Plans</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/employer?zg=false</t>
+  </si>
+  <si>
     <t>index.report.json</t>
   </si>
   <si>
@@ -46,13 +70,10 @@
     <t>index</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>home</t>
   </si>
   <si>
-    <t>2026-08-18T01:04:26.065Z</t>
+    <t>2026-09-30T16:04:26.807Z</t>
   </si>
   <si>
     <t>Highmark: Health Insurance Plans for Individuals &amp; Businesses</t>
@@ -82,6 +103,99 @@
     <t>https://www.highmark.com/resources</t>
   </si>
   <si>
+    <t>employer/care-management.report.json</t>
+  </si>
+  <si>
+    <t>["columns-minimal-dark","columns-minimal-dark","columns-minimal-dark","columns-minimal-dark"]</t>
+  </si>
+  <si>
+    <t>employer/care-management</t>
+  </si>
+  <si>
+    <t>employer-subpage</t>
+  </si>
+  <si>
+    <t>2026-09-30T17:19:36.476Z</t>
+  </si>
+  <si>
+    <t>Highmark Offers Employee Health Care Management Solutions</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/employer/care-management?zg=false</t>
+  </si>
+  <si>
+    <t>employer/client-resources.report.json</t>
+  </si>
+  <si>
+    <t>["columns-minimal-dark","columns-minimal-dark","columns-minimal-dark"]</t>
+  </si>
+  <si>
+    <t>employer/client-resources</t>
+  </si>
+  <si>
+    <t>2026-09-30T17:19:42.300Z</t>
+  </si>
+  <si>
+    <t>Client Resources for Highmark Employer Health Plans</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/employer/client-resources?zg=false</t>
+  </si>
+  <si>
+    <t>employer/cost-management.report.json</t>
+  </si>
+  <si>
+    <t>["columns-minimal-dark","columns-minimal-dark","columns-minimal-dark","columns-minimal-dark","cards-minimal-dark-withimg-icons"]</t>
+  </si>
+  <si>
+    <t>employer/cost-management</t>
+  </si>
+  <si>
+    <t>2026-09-30T17:19:29.603Z</t>
+  </si>
+  <si>
+    <t>Protect Your Self-Funded Health Care with Stop Loss Coverage.</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/employer/cost-management?zg=false</t>
+  </si>
+  <si>
+    <t>employer/solutions.report.json</t>
+  </si>
+  <si>
+    <t>["cards-minimal-dark-withimg-icons"]</t>
+  </si>
+  <si>
+    <t>employer/solutions</t>
+  </si>
+  <si>
+    <t>2026-09-30T17:19:47.754Z</t>
+  </si>
+  <si>
+    <t>Highmark Business Solutions: Find the Right Plan for You</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/employer/solutions?zg=false</t>
+  </si>
+  <si>
+    <t>employer/thought-leadership.report.json</t>
+  </si>
+  <si>
+    <t>["columns-minimal-dark","cards-minimal-dark-iconnav","cards-minimal-dark-withimg"]</t>
+  </si>
+  <si>
+    <t>employer/thought-leadership</t>
+  </si>
+  <si>
+    <t>2026-09-30T17:19:52.087Z</t>
+  </si>
+  <si>
+    <t>Thought Leadership Articles and Information | Highmark</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/employer/thought-leadership?zg=false</t>
+  </si>
+  <si>
     <t>plans/d-snp.report.json</t>
   </si>
   <si>
@@ -94,7 +208,7 @@
     <t>state-plans</t>
   </si>
   <si>
-    <t>2026-09-30T15:28:04.778Z</t>
+    <t>2026-09-30T17:20:00.413Z</t>
   </si>
   <si>
     <t>Dual Eligible Special Needs Plans (D-SNP)</t>
@@ -115,7 +229,7 @@
     <t>plans</t>
   </si>
   <si>
-    <t>2026-09-29T14:12:56.610Z</t>
+    <t>2026-09-30T16:04:35.898Z</t>
   </si>
   <si>
     <t>Affordable ACA Health Insurance Plans for Individuals and Families</t>
@@ -130,7 +244,7 @@
     <t>plans/medicaid</t>
   </si>
   <si>
-    <t>2026-09-30T15:28:13.373Z</t>
+    <t>2026-09-30T17:20:06.891Z</t>
   </si>
   <si>
     <t>Medicaid</t>
@@ -151,7 +265,7 @@
     <t>tabbed-answers-landing</t>
   </si>
   <si>
-    <t>2026-08-17T23:05:17.790Z</t>
+    <t>2026-09-30T16:16:40.093Z</t>
   </si>
   <si>
     <t>Highmark Answers: Health Insurance FAQs &amp; More</t>
@@ -169,7 +283,7 @@
     <t>resources/mental-health-services</t>
   </si>
   <si>
-    <t>2026-08-17T19:00:16.792Z</t>
+    <t>2026-09-30T16:05:29.090Z</t>
   </si>
   <si>
     <t>Mental Health Services | Highmark</t>
@@ -190,7 +304,7 @@
     <t>topic-hub-subnav</t>
   </si>
   <si>
-    <t>2026-09-30T13:53:17.011Z</t>
+    <t>2026-09-30T16:16:15.127Z</t>
   </si>
   <si>
     <t>All About Spending Accounts: FSA, HSA, HRA | Highmark</t>
@@ -211,7 +325,7 @@
     <t>chip-landing</t>
   </si>
   <si>
-    <t>2026-09-29T21:31:20.155Z</t>
+    <t>2026-09-30T16:04:45.466Z</t>
   </si>
   <si>
     <t>CHIP - Highmark Healthy Kids | Highmark Blue Cross Blue Shield</t>
@@ -220,6 +334,27 @@
     <t>https://www.highmark.com/western-pennsylvania/chip?zg=false</t>
   </si>
   <si>
+    <t>member/member-guide/find-care.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","cards-minimal-dark-list"]</t>
+  </si>
+  <si>
+    <t>member/member-guide/find-care</t>
+  </si>
+  <si>
+    <t>find-care</t>
+  </si>
+  <si>
+    <t>2026-09-30T16:06:59.548Z</t>
+  </si>
+  <si>
+    <t>Find Care - Find a Provider | Highmark</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/member/member-guide/find-care?zg=false</t>
+  </si>
+  <si>
     <t>plans/individual-families/get-help.report.json</t>
   </si>
   <si>
@@ -232,7 +367,7 @@
     <t>get-help</t>
   </si>
   <si>
-    <t>2026-09-30T15:28:30.018Z</t>
+    <t>2026-09-30T17:20:20.435Z</t>
   </si>
   <si>
     <t>Get Help Choosing a ACA Plan | Highmark ACA Specialists</t>
@@ -241,6 +376,27 @@
     <t>https://www.highmark.com/plans/individual-families/get-help?zg=false</t>
   </si>
   <si>
+    <t>plans/medicare/blue-neighbors.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","columns-minimal-dark","columns-minimal-dark","cards-minimal-dark-list","cards-minimal-dark-withimg-2"]</t>
+  </si>
+  <si>
+    <t>plans/medicare/blue-neighbors</t>
+  </si>
+  <si>
+    <t>blue-neighbors</t>
+  </si>
+  <si>
+    <t>2026-09-30T16:15:48.958Z</t>
+  </si>
+  <si>
+    <t>Blue Neighbors - Volunteers for Seniors | Highmark</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/plans/medicare/blue-neighbors?zg=false</t>
+  </si>
+  <si>
     <t>plans/medicare/get-help.report.json</t>
   </si>
   <si>
@@ -250,7 +406,7 @@
     <t>plans/medicare/get-help</t>
   </si>
   <si>
-    <t>2026-09-30T15:28:22.835Z</t>
+    <t>2026-09-30T17:20:15.030Z</t>
   </si>
   <si>
     <t>Get Help Choosing a Medicare Plan | Highmark Medicare Specialists</t>
@@ -271,7 +427,7 @@
     <t>learn-about-medicare</t>
   </si>
   <si>
-    <t>2026-09-30T15:28:38.509Z</t>
+    <t>2026-09-30T17:20:29.543Z</t>
   </si>
   <si>
     <t>Learn About Medicare | Highmark</t>
@@ -343,7 +499,7 @@
     <t>resources/answers/health-insurance-glossary</t>
   </si>
   <si>
-    <t>2026-08-17T23:05:24.936Z</t>
+    <t>2026-09-30T16:16:45.955Z</t>
   </si>
   <si>
     <t>Health Insurance Glossary | Highmark</t>
@@ -361,7 +517,7 @@
     <t>resources/mental-health-services/anxiety</t>
   </si>
   <si>
-    <t>2026-09-30T13:52:58.519Z</t>
+    <t>2026-09-30T16:15:57.349Z</t>
   </si>
   <si>
     <t>Anxiety Warning Signs, Types and Treatments | Highmark</t>
@@ -376,7 +532,7 @@
     <t>resources/mental-health-services/depression</t>
   </si>
   <si>
-    <t>2026-09-30T13:53:04.310Z</t>
+    <t>2026-09-30T16:16:03.390Z</t>
   </si>
   <si>
     <t>Depression| Highmark</t>
@@ -391,7 +547,7 @@
     <t>resources/mental-health-services/eating-disorders</t>
   </si>
   <si>
-    <t>2026-09-30T13:53:10.806Z</t>
+    <t>2026-09-30T16:16:08.642Z</t>
   </si>
   <si>
     <t>Eating Disorders | Highmark</t>
@@ -409,7 +565,7 @@
     <t>resources/mental-health-services/mental-health-resources-teens-children</t>
   </si>
   <si>
-    <t>2026-09-30T13:53:31.088Z</t>
+    <t>2026-09-30T16:16:25.408Z</t>
   </si>
   <si>
     <t>Mental Health Resources for Teens and Children | Highmark</t>
@@ -427,7 +583,7 @@
     <t>resources/mental-health-services/mental-health-resources</t>
   </si>
   <si>
-    <t>2026-09-30T13:53:37.087Z</t>
+    <t>2026-09-30T16:16:31.446Z</t>
   </si>
   <si>
     <t>Mental Health Resources | Highmark</t>
@@ -442,7 +598,7 @@
     <t>resources/mental-health-services/substance-use-disorders</t>
   </si>
   <si>
-    <t>2026-09-30T13:53:24.441Z</t>
+    <t>2026-09-30T16:16:21.075Z</t>
   </si>
   <si>
     <t>Substance Use Disorders | Highmark</t>
@@ -478,7 +634,7 @@
     <t>resources/spending-accounts/commuter-benefits-account</t>
   </si>
   <si>
-    <t>2026-08-17T23:05:31.409Z</t>
+    <t>2026-09-30T16:16:50.299Z</t>
   </si>
   <si>
     <t>Commuter Benefits Account | Highmark</t>
@@ -496,7 +652,7 @@
     <t>resources/spending-accounts/flexible-spending-account-fsa</t>
   </si>
   <si>
-    <t>2026-08-17T23:05:37.551Z</t>
+    <t>2026-09-30T16:16:55.215Z</t>
   </si>
   <si>
     <t>Flexible Spending Accounts (FSA) | Highmark</t>
@@ -511,7 +667,7 @@
     <t>resources/spending-accounts/health-reimbursement-arrangement-hra</t>
   </si>
   <si>
-    <t>2026-08-18T00:38:30.941Z</t>
+    <t>2026-09-30T16:17:04.251Z</t>
   </si>
   <si>
     <t>Health Reimbursement Arrangement (HRA) | Highmark</t>
@@ -526,7 +682,7 @@
     <t>resources/spending-accounts/health-saving-account-hsa</t>
   </si>
   <si>
-    <t>2026-08-17T23:05:43.527Z</t>
+    <t>2026-09-30T16:17:00.349Z</t>
   </si>
   <si>
     <t>Health Savings Account (HSA) | Highmark</t>
@@ -1374,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -1518,42 +1674,42 @@
         <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
         <v>46</v>
@@ -1579,7 +1735,7 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
         <v>52</v>
@@ -1605,189 +1761,189 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" t="s">
         <v>58</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>59</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>60</v>
-      </c>
-      <c r="H9" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
         <v>62</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>63</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
         <v>64</v>
       </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>65</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>66</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>67</v>
-      </c>
-      <c r="H10" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
         <v>69</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>70</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
         <v>71</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>72</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>73</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>74</v>
-      </c>
-      <c r="H11" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
         <v>76</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
         <v>77</v>
       </c>
-      <c r="C12" t="s">
+      <c r="G12" t="s">
         <v>78</v>
       </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>79</v>
-      </c>
-      <c r="G12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
         <v>82</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
         <v>83</v>
       </c>
-      <c r="C13" t="s">
+      <c r="F13" t="s">
         <v>84</v>
       </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>85</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
         <v>86</v>
-      </c>
-      <c r="G13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
         <v>89</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
         <v>90</v>
       </c>
-      <c r="C14" t="s">
+      <c r="G14" t="s">
         <v>91</v>
       </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="H14" t="s">
         <v>92</v>
-      </c>
-      <c r="F14" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" t="s">
-        <v>94</v>
-      </c>
-      <c r="H14" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
         <v>96</v>
       </c>
-      <c r="B15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="F15" t="s">
         <v>97</v>
       </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>98</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>99</v>
-      </c>
-      <c r="H15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s">
         <v>101</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>102</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
         <v>103</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>92</v>
       </c>
       <c r="F16" t="s">
         <v>104</v>
@@ -1813,1030 +1969,1238 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="F17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="F18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G18" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="F19" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G19" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H19" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="F20" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G20" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H20" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="F21" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G21" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H21" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B22" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F22" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="H22" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="C23" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F23" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G23" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H23" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="C24" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F24" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G24" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H24" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C25" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F25" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G25" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G26" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H26" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B27" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="F27" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="G27" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H27" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B28" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="F28" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="G28" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H28" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C29" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="F29" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="G29" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="H29" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C30" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="F30" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G30" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H30" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B31" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="C31" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="G31" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H31" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B32" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="F32" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G32" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="H32" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B33" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C33" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="G33" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H33" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="C34" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="F34" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="G34" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="H34" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B35" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C35" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F35" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="G35" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="H35" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B36" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C36" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="F36" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G36" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H36" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>227</v>
       </c>
       <c r="C37" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>92</v>
+        <v>229</v>
       </c>
       <c r="F37" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="G37" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H37" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B38" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C38" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
         <v>229</v>
       </c>
-      <c r="D38" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" t="s">
-        <v>92</v>
-      </c>
       <c r="F38" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G38" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="H38" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B39" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="C39" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>92</v>
+        <v>229</v>
       </c>
       <c r="F39" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G39" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H39" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>234</v>
       </c>
       <c r="C40" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>92</v>
+        <v>229</v>
       </c>
       <c r="F40" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G40" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="H40" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B41" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="C41" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>92</v>
+        <v>229</v>
       </c>
       <c r="F41" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="G41" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="H41" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B42" t="s">
-        <v>249</v>
+        <v>142</v>
       </c>
       <c r="C42" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="F42" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="G42" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H42" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B43" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="C43" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="F43" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="G43" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="H43" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B44" t="s">
-        <v>210</v>
+        <v>268</v>
       </c>
       <c r="C44" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>92</v>
+        <v>270</v>
       </c>
       <c r="F44" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="G44" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="H44" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B45" t="s">
-        <v>216</v>
+        <v>154</v>
       </c>
       <c r="C45" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="F45" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="G45" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="H45" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B46" t="s">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="C46" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="F46" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="G46" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="H46" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B47" t="s">
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>276</v>
+        <v>144</v>
       </c>
       <c r="F47" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="G47" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="H47" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B48" t="s">
-        <v>216</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>218</v>
+        <v>144</v>
       </c>
       <c r="F48" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="G48" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="H48" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B49" t="s">
-        <v>216</v>
+        <v>268</v>
       </c>
       <c r="C49" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="F49" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="G49" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="H49" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B50" t="s">
-        <v>210</v>
+        <v>301</v>
       </c>
       <c r="C50" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F50" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="G50" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="H50" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>268</v>
       </c>
       <c r="C51" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F51" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="G51" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="H51" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>262</v>
       </c>
       <c r="C52" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F52" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="G52" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="H52" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="B53" t="s">
-        <v>90</v>
+        <v>268</v>
       </c>
       <c r="C53" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
       </c>
       <c r="E53" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F53" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="G53" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="H53" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>268</v>
       </c>
       <c r="C54" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F54" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="G54" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="H54" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>262</v>
       </c>
       <c r="C55" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>205</v>
+        <v>328</v>
       </c>
       <c r="F55" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="G55" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="H55" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>268</v>
       </c>
       <c r="C56" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="F56" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G56" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="H56" t="s">
-        <v>324</v>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>337</v>
+      </c>
+      <c r="B57" t="s">
+        <v>268</v>
+      </c>
+      <c r="C57" t="s">
+        <v>338</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>144</v>
+      </c>
+      <c r="F57" t="s">
+        <v>339</v>
+      </c>
+      <c r="G57" t="s">
+        <v>340</v>
+      </c>
+      <c r="H57" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>342</v>
+      </c>
+      <c r="B58" t="s">
+        <v>262</v>
+      </c>
+      <c r="C58" t="s">
+        <v>343</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" t="s">
+        <v>328</v>
+      </c>
+      <c r="F58" t="s">
+        <v>344</v>
+      </c>
+      <c r="G58" t="s">
+        <v>345</v>
+      </c>
+      <c r="H58" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>347</v>
+      </c>
+      <c r="B59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" t="s">
+        <v>348</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" t="s">
+        <v>200</v>
+      </c>
+      <c r="F59" t="s">
+        <v>349</v>
+      </c>
+      <c r="G59" t="s">
+        <v>350</v>
+      </c>
+      <c r="H59" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>352</v>
+      </c>
+      <c r="B60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" t="s">
+        <v>353</v>
+      </c>
+      <c r="D60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" t="s">
+        <v>200</v>
+      </c>
+      <c r="F60" t="s">
+        <v>354</v>
+      </c>
+      <c r="G60" t="s">
+        <v>355</v>
+      </c>
+      <c r="H60" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>357</v>
+      </c>
+      <c r="B61" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" t="s">
+        <v>358</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>200</v>
+      </c>
+      <c r="F61" t="s">
+        <v>359</v>
+      </c>
+      <c r="G61" t="s">
+        <v>360</v>
+      </c>
+      <c r="H61" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>362</v>
+      </c>
+      <c r="B62" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" t="s">
+        <v>363</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" t="s">
+        <v>200</v>
+      </c>
+      <c r="F62" t="s">
+        <v>364</v>
+      </c>
+      <c r="G62" t="s">
+        <v>365</v>
+      </c>
+      <c r="H62" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>367</v>
+      </c>
+      <c r="B63" t="s">
+        <v>142</v>
+      </c>
+      <c r="C63" t="s">
+        <v>368</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>257</v>
+      </c>
+      <c r="F63" t="s">
+        <v>369</v>
+      </c>
+      <c r="G63" t="s">
+        <v>370</v>
+      </c>
+      <c r="H63" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>372</v>
+      </c>
+      <c r="B64" t="s">
+        <v>142</v>
+      </c>
+      <c r="C64" t="s">
+        <v>373</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>200</v>
+      </c>
+      <c r="F64" t="s">
+        <v>374</v>
+      </c>
+      <c r="G64" t="s">
+        <v>375</v>
+      </c>
+      <c r="H64" t="s">
+        <v>376</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-learn-about-medicare.report.xlsx
+++ b/tools/importer/reports/import-learn-about-medicare.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="427">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>employer-landing</t>
   </si>
   <si>
-    <t>2026-09-30T17:19:21.302Z</t>
+    <t>2026-09-30T17:51:29.928Z</t>
   </si>
   <si>
     <t>Boost Employee Health and Save Money with Highmark Employer Plans</t>
@@ -103,6 +103,42 @@
     <t>https://www.highmark.com/resources</t>
   </si>
   <si>
+    <t>about/corporate-responsibility.report.json</t>
+  </si>
+  <si>
+    <t>["cards-minimal-light-sidenav","cards-minimal-light-sidenav"]</t>
+  </si>
+  <si>
+    <t>about/corporate-responsibility</t>
+  </si>
+  <si>
+    <t>about-article</t>
+  </si>
+  <si>
+    <t>2026-09-30T18:08:29.686Z</t>
+  </si>
+  <si>
+    <t>Corporate Responsibility | Highmark</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/corporate-responsibility?zg=false</t>
+  </si>
+  <si>
+    <t>about/our-story.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story</t>
+  </si>
+  <si>
+    <t>2026-09-30T18:08:10.569Z</t>
+  </si>
+  <si>
+    <t>Highmark: Our Story</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story?zg=false</t>
+  </si>
+  <si>
     <t>employer/care-management.report.json</t>
   </si>
   <si>
@@ -208,7 +244,7 @@
     <t>state-plans</t>
   </si>
   <si>
-    <t>2026-09-30T17:20:00.413Z</t>
+    <t>2026-09-30T18:19:58.716Z</t>
   </si>
   <si>
     <t>Dual Eligible Special Needs Plans (D-SNP)</t>
@@ -244,7 +280,7 @@
     <t>plans/medicaid</t>
   </si>
   <si>
-    <t>2026-09-30T17:20:06.891Z</t>
+    <t>2026-09-30T18:20:04.342Z</t>
   </si>
   <si>
     <t>Medicaid</t>
@@ -334,6 +370,123 @@
     <t>https://www.highmark.com/western-pennsylvania/chip?zg=false</t>
   </si>
   <si>
+    <t>about/corporate-responsibility/bright-blue-futures.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","columns-minimal-dark","columns-minimal-dark","columns-minimal-dark","columns-minimal-dark","cards-minimal-dark-withimg-icons","cards-minimal-dark-withimg-2"]</t>
+  </si>
+  <si>
+    <t>about/corporate-responsibility/bright-blue-futures</t>
+  </si>
+  <si>
+    <t>bright-blue-futures</t>
+  </si>
+  <si>
+    <t>2026-09-30T18:19:49.316Z</t>
+  </si>
+  <si>
+    <t>Highmark Bright Blue Futures | Corporate Giving</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/corporate-responsibility/bright-blue-futures?zg=false</t>
+  </si>
+  <si>
+    <t>about/corporate-responsibility/social-determinants-of-health.report.json</t>
+  </si>
+  <si>
+    <t>about/corporate-responsibility/social-determinants-of-health</t>
+  </si>
+  <si>
+    <t>2026-09-30T18:08:41.043Z</t>
+  </si>
+  <si>
+    <t>Social Determinants of Health (SDoH)</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/corporate-responsibility/social-determinants-of-health?zg=false</t>
+  </si>
+  <si>
+    <t>about/corporate-responsibility/sustainability.report.json</t>
+  </si>
+  <si>
+    <t>about/corporate-responsibility/sustainability</t>
+  </si>
+  <si>
+    <t>2026-09-30T18:08:46.681Z</t>
+  </si>
+  <si>
+    <t>Highmark Sustainability: Our Commitment to a Healthier Future</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/corporate-responsibility/sustainability?zg=false</t>
+  </si>
+  <si>
+    <t>about/corporate-responsibility/valuing-our-people.report.json</t>
+  </si>
+  <si>
+    <t>about/corporate-responsibility/valuing-our-people</t>
+  </si>
+  <si>
+    <t>2026-09-30T18:08:34.679Z</t>
+  </si>
+  <si>
+    <t>Highmark Health: Valuing Our People</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/corporate-responsibility/valuing-our-people?zg=false</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board.report.json</t>
+  </si>
+  <si>
+    <t>["cards-minimal-light-sidenav","cards-minimal-light-sidenav","cards-minimal-dark-withimg","cards-minimal-dark-withimg"]</t>
+  </si>
+  <si>
+    <t>about/our-story/leadership-team-board</t>
+  </si>
+  <si>
+    <t>leadership</t>
+  </si>
+  <si>
+    <t>2026-09-30T18:12:42.349Z</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/leadership-team-board?zg=false</t>
+  </si>
+  <si>
+    <t>about/our-story/mission-vision.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/mission-vision</t>
+  </si>
+  <si>
+    <t>2026-09-30T18:08:16.965Z</t>
+  </si>
+  <si>
+    <t>Mission, Vision, &amp; Core Behaviors</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/mission-vision?zg=false</t>
+  </si>
+  <si>
+    <t>about/our-story/our-businesses.report.json</t>
+  </si>
+  <si>
+    <t>about/our-story/our-businesses</t>
+  </si>
+  <si>
+    <t>2026-09-30T18:08:23.116Z</t>
+  </si>
+  <si>
+    <t>Highmark Health: Our Diverse Businesses and Affiliates</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/about/our-story/our-businesses?zg=false</t>
+  </si>
+  <si>
     <t>member/member-guide/find-care.report.json</t>
   </si>
   <si>
@@ -346,7 +499,7 @@
     <t>find-care</t>
   </si>
   <si>
-    <t>2026-09-30T16:06:59.548Z</t>
+    <t>2026-09-30T17:20:46.063Z</t>
   </si>
   <si>
     <t>Find Care - Find a Provider | Highmark</t>
@@ -367,7 +520,7 @@
     <t>get-help</t>
   </si>
   <si>
-    <t>2026-09-30T17:20:20.435Z</t>
+    <t>2026-09-30T18:20:20.581Z</t>
   </si>
   <si>
     <t>Get Help Choosing a ACA Plan | Highmark ACA Specialists</t>
@@ -388,7 +541,7 @@
     <t>blue-neighbors</t>
   </si>
   <si>
-    <t>2026-09-30T16:15:48.958Z</t>
+    <t>2026-09-30T17:20:37.848Z</t>
   </si>
   <si>
     <t>Blue Neighbors - Volunteers for Seniors | Highmark</t>
@@ -406,7 +559,7 @@
     <t>plans/medicare/get-help</t>
   </si>
   <si>
-    <t>2026-09-30T17:20:15.030Z</t>
+    <t>2026-09-30T18:20:14.588Z</t>
   </si>
   <si>
     <t>Get Help Choosing a Medicare Plan | Highmark Medicare Specialists</t>
@@ -427,7 +580,7 @@
     <t>learn-about-medicare</t>
   </si>
   <si>
-    <t>2026-09-30T17:20:29.543Z</t>
+    <t>2026-09-30T18:20:29.993Z</t>
   </si>
   <si>
     <t>Learn About Medicare | Highmark</t>
@@ -437,9 +590,6 @@
   </si>
   <si>
     <t>resources/answers/articles.report.json</t>
-  </si>
-  <si>
-    <t>["cards-minimal-light-sidenav","cards-minimal-light-sidenav"]</t>
   </si>
   <si>
     <t>resources/answers/articles</t>
@@ -1530,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -1674,10 +1824,10 @@
         <v>37</v>
       </c>
       <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
         <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -1686,30 +1836,30 @@
         <v>33</v>
       </c>
       <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
         <v>40</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>41</v>
-      </c>
-      <c r="H6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>44</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
         <v>45</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
       </c>
       <c r="F7" t="s">
         <v>46</v>
@@ -1735,7 +1885,7 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
         <v>52</v>
@@ -1761,7 +1911,7 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
         <v>58</v>
@@ -1787,59 +1937,59 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" t="s">
         <v>64</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>65</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>66</v>
-      </c>
-      <c r="H10" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
         <v>68</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>69</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
         <v>70</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>71</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>72</v>
-      </c>
-      <c r="G11" t="s">
-        <v>73</v>
-      </c>
-      <c r="H11" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
         <v>75</v>
       </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
         <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>64</v>
       </c>
       <c r="F12" t="s">
         <v>77</v>
@@ -1882,244 +2032,244 @@
         <v>87</v>
       </c>
       <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
         <v>88</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s">
         <v>89</v>
       </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>90</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>91</v>
-      </c>
-      <c r="H14" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" t="s">
         <v>93</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>94</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
         <v>95</v>
       </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>96</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>97</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>98</v>
-      </c>
-      <c r="H15" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
         <v>100</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>101</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
         <v>102</v>
       </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>103</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>104</v>
-      </c>
-      <c r="G16" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
         <v>107</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
         <v>108</v>
       </c>
-      <c r="C17" t="s">
+      <c r="F17" t="s">
         <v>109</v>
       </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>110</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
         <v>111</v>
-      </c>
-      <c r="G17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H17" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" t="s">
         <v>114</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
         <v>115</v>
       </c>
-      <c r="C18" t="s">
+      <c r="F18" t="s">
         <v>116</v>
       </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>117</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>118</v>
-      </c>
-      <c r="G18" t="s">
-        <v>119</v>
-      </c>
-      <c r="H18" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" t="s">
         <v>121</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
         <v>122</v>
       </c>
-      <c r="C19" t="s">
+      <c r="F19" t="s">
         <v>123</v>
       </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>124</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>125</v>
-      </c>
-      <c r="G19" t="s">
-        <v>126</v>
-      </c>
-      <c r="H19" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" t="s">
         <v>128</v>
       </c>
-      <c r="B20" t="s">
+      <c r="G20" t="s">
         <v>129</v>
       </c>
-      <c r="C20" t="s">
+      <c r="H20" t="s">
         <v>130</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" t="s">
-        <v>117</v>
-      </c>
-      <c r="F20" t="s">
-        <v>131</v>
-      </c>
-      <c r="G20" t="s">
-        <v>132</v>
-      </c>
-      <c r="H20" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G21" t="s">
         <v>134</v>
       </c>
-      <c r="B21" t="s">
+      <c r="H21" t="s">
         <v>135</v>
-      </c>
-      <c r="C21" t="s">
-        <v>136</v>
-      </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" t="s">
-        <v>137</v>
-      </c>
-      <c r="F21" t="s">
-        <v>138</v>
-      </c>
-      <c r="G21" t="s">
-        <v>139</v>
-      </c>
-      <c r="H21" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>144</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G22" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H22" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B23" t="s">
         <v>142</v>
       </c>
       <c r="C23" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -2128,212 +2278,212 @@
         <v>144</v>
       </c>
       <c r="F23" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G23" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H23" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>144</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G24" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H24" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G25" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="H25" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="F26" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G26" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H26" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B27" t="s">
         <v>166</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="F27" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H27" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>175</v>
+      </c>
+      <c r="F28" t="s">
         <v>176</v>
       </c>
-      <c r="B28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="G28" t="s">
         <v>177</v>
       </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" t="s">
-        <v>96</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="H28" t="s">
         <v>178</v>
-      </c>
-      <c r="G28" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>179</v>
+      </c>
+      <c r="B29" t="s">
+        <v>180</v>
+      </c>
+      <c r="C29" t="s">
         <v>181</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>168</v>
+      </c>
+      <c r="F29" t="s">
         <v>182</v>
       </c>
-      <c r="C29" t="s">
+      <c r="G29" t="s">
         <v>183</v>
       </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>96</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="H29" t="s">
         <v>184</v>
-      </c>
-      <c r="G29" t="s">
-        <v>185</v>
-      </c>
-      <c r="H29" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>185</v>
+      </c>
+      <c r="B30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" t="s">
         <v>187</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
         <v>188</v>
       </c>
-      <c r="C30" t="s">
+      <c r="F30" t="s">
         <v>189</v>
       </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>190</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>191</v>
-      </c>
-      <c r="H30" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>192</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" t="s">
         <v>193</v>
       </c>
-      <c r="B31" t="s">
-        <v>166</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
         <v>194</v>
-      </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" t="s">
-        <v>96</v>
       </c>
       <c r="F31" t="s">
         <v>195</v>
@@ -2350,7 +2500,7 @@
         <v>198</v>
       </c>
       <c r="B32" t="s">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
         <v>199</v>
@@ -2359,76 +2509,76 @@
         <v>11</v>
       </c>
       <c r="E32" t="s">
+        <v>194</v>
+      </c>
+      <c r="F32" t="s">
         <v>200</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>201</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>202</v>
-      </c>
-      <c r="H32" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" t="s">
         <v>204</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>205</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>194</v>
+      </c>
+      <c r="F33" t="s">
         <v>206</v>
       </c>
-      <c r="D33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" t="s">
-        <v>83</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>207</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>208</v>
-      </c>
-      <c r="H33" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>209</v>
+      </c>
+      <c r="B34" t="s">
         <v>210</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>211</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>95</v>
+      </c>
+      <c r="F34" t="s">
         <v>212</v>
       </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" t="s">
-        <v>83</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>213</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>214</v>
-      </c>
-      <c r="H34" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" t="s">
         <v>216</v>
-      </c>
-      <c r="B35" t="s">
-        <v>205</v>
       </c>
       <c r="C35" t="s">
         <v>217</v>
@@ -2437,7 +2587,7 @@
         <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="F35" t="s">
         <v>218</v>
@@ -2454,7 +2604,7 @@
         <v>221</v>
       </c>
       <c r="B36" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C36" t="s">
         <v>222</v>
@@ -2463,7 +2613,7 @@
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="F36" t="s">
         <v>223</v>
@@ -2480,137 +2630,137 @@
         <v>226</v>
       </c>
       <c r="B37" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37" t="s">
         <v>227</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" t="s">
         <v>228</v>
       </c>
-      <c r="D37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>229</v>
       </c>
-      <c r="F37" t="s">
+      <c r="H37" t="s">
         <v>230</v>
-      </c>
-      <c r="G37" t="s">
-        <v>231</v>
-      </c>
-      <c r="H37" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>231</v>
+      </c>
+      <c r="B38" t="s">
+        <v>232</v>
+      </c>
+      <c r="C38" t="s">
         <v>233</v>
       </c>
-      <c r="B38" t="s">
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" t="s">
         <v>234</v>
       </c>
-      <c r="C38" t="s">
+      <c r="G38" t="s">
         <v>235</v>
       </c>
-      <c r="D38" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" t="s">
-        <v>229</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="H38" t="s">
         <v>236</v>
-      </c>
-      <c r="G38" t="s">
-        <v>237</v>
-      </c>
-      <c r="H38" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>237</v>
+      </c>
+      <c r="B39" t="s">
+        <v>238</v>
+      </c>
+      <c r="C39" t="s">
         <v>239</v>
       </c>
-      <c r="B39" t="s">
-        <v>234</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>108</v>
+      </c>
+      <c r="F39" t="s">
         <v>240</v>
       </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" t="s">
-        <v>229</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>241</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>242</v>
-      </c>
-      <c r="H39" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>243</v>
+      </c>
+      <c r="B40" t="s">
+        <v>216</v>
+      </c>
+      <c r="C40" t="s">
         <v>244</v>
       </c>
-      <c r="B40" t="s">
-        <v>234</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>108</v>
+      </c>
+      <c r="F40" t="s">
         <v>245</v>
       </c>
-      <c r="D40" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" t="s">
-        <v>229</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>246</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>247</v>
-      </c>
-      <c r="H40" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>248</v>
+      </c>
+      <c r="B41" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" t="s">
         <v>249</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
         <v>250</v>
       </c>
-      <c r="C41" t="s">
+      <c r="F41" t="s">
         <v>251</v>
       </c>
-      <c r="D41" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" t="s">
-        <v>229</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>252</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>253</v>
-      </c>
-      <c r="H41" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>254</v>
+      </c>
+      <c r="B42" t="s">
         <v>255</v>
-      </c>
-      <c r="B42" t="s">
-        <v>142</v>
       </c>
       <c r="C42" t="s">
         <v>256</v>
@@ -2619,241 +2769,241 @@
         <v>11</v>
       </c>
       <c r="E42" t="s">
+        <v>95</v>
+      </c>
+      <c r="F42" t="s">
         <v>257</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>258</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>259</v>
-      </c>
-      <c r="H42" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>260</v>
+      </c>
+      <c r="B43" t="s">
         <v>261</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>262</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>95</v>
+      </c>
+      <c r="F43" t="s">
         <v>263</v>
       </c>
-      <c r="D43" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" t="s">
-        <v>144</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>264</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>265</v>
-      </c>
-      <c r="H43" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>266</v>
+      </c>
+      <c r="B44" t="s">
+        <v>255</v>
+      </c>
+      <c r="C44" t="s">
         <v>267</v>
       </c>
-      <c r="B44" t="s">
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>95</v>
+      </c>
+      <c r="F44" t="s">
         <v>268</v>
       </c>
-      <c r="C44" t="s">
+      <c r="G44" t="s">
         <v>269</v>
       </c>
-      <c r="D44" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="H44" t="s">
         <v>270</v>
-      </c>
-      <c r="F44" t="s">
-        <v>271</v>
-      </c>
-      <c r="G44" t="s">
-        <v>272</v>
-      </c>
-      <c r="H44" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>271</v>
+      </c>
+      <c r="B45" t="s">
+        <v>261</v>
+      </c>
+      <c r="C45" t="s">
+        <v>272</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F45" t="s">
+        <v>273</v>
+      </c>
+      <c r="G45" t="s">
         <v>274</v>
       </c>
-      <c r="B45" t="s">
-        <v>154</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="H45" t="s">
         <v>275</v>
-      </c>
-      <c r="D45" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" t="s">
-        <v>144</v>
-      </c>
-      <c r="F45" t="s">
-        <v>276</v>
-      </c>
-      <c r="G45" t="s">
-        <v>277</v>
-      </c>
-      <c r="H45" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>276</v>
+      </c>
+      <c r="B46" t="s">
+        <v>277</v>
+      </c>
+      <c r="C46" t="s">
+        <v>278</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
         <v>279</v>
       </c>
-      <c r="B46" t="s">
+      <c r="F46" t="s">
         <v>280</v>
       </c>
-      <c r="C46" t="s">
+      <c r="G46" t="s">
         <v>281</v>
       </c>
-      <c r="D46" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" t="s">
-        <v>144</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="H46" t="s">
         <v>282</v>
-      </c>
-      <c r="G46" t="s">
-        <v>283</v>
-      </c>
-      <c r="H46" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>283</v>
+      </c>
+      <c r="B47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C47" t="s">
         <v>285</v>
       </c>
-      <c r="B47" t="s">
-        <v>262</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>279</v>
+      </c>
+      <c r="F47" t="s">
         <v>286</v>
       </c>
-      <c r="D47" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" t="s">
-        <v>144</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>287</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>288</v>
-      </c>
-      <c r="H47" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>289</v>
+      </c>
+      <c r="B48" t="s">
+        <v>284</v>
+      </c>
+      <c r="C48" t="s">
         <v>290</v>
       </c>
-      <c r="B48" t="s">
-        <v>142</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>279</v>
+      </c>
+      <c r="F48" t="s">
         <v>291</v>
       </c>
-      <c r="D48" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" t="s">
-        <v>144</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>292</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>293</v>
-      </c>
-      <c r="H48" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>294</v>
+      </c>
+      <c r="B49" t="s">
+        <v>284</v>
+      </c>
+      <c r="C49" t="s">
         <v>295</v>
       </c>
-      <c r="B49" t="s">
-        <v>268</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F49" t="s">
         <v>296</v>
       </c>
-      <c r="D49" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" t="s">
-        <v>144</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>297</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>298</v>
-      </c>
-      <c r="H49" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>299</v>
+      </c>
+      <c r="B50" t="s">
         <v>300</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>301</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>279</v>
+      </c>
+      <c r="F50" t="s">
         <v>302</v>
       </c>
-      <c r="D50" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" t="s">
-        <v>270</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>303</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>304</v>
-      </c>
-      <c r="H50" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>305</v>
+      </c>
+      <c r="B51" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" t="s">
         <v>306</v>
       </c>
-      <c r="B51" t="s">
-        <v>268</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
         <v>307</v>
-      </c>
-      <c r="D51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" t="s">
-        <v>144</v>
       </c>
       <c r="F51" t="s">
         <v>308</v>
@@ -2870,337 +3020,571 @@
         <v>311</v>
       </c>
       <c r="B52" t="s">
-        <v>262</v>
+        <v>312</v>
       </c>
       <c r="C52" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="F52" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B53" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
       <c r="C53" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
       </c>
       <c r="E53" t="s">
-        <v>144</v>
+        <v>320</v>
       </c>
       <c r="F53" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G53" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H53" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B54" t="s">
-        <v>268</v>
+        <v>204</v>
       </c>
       <c r="C54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="F54" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G54" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H54" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B55" t="s">
-        <v>262</v>
+        <v>330</v>
       </c>
       <c r="C55" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>328</v>
+        <v>194</v>
       </c>
       <c r="F55" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G55" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="H55" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B56" t="s">
-        <v>268</v>
+        <v>312</v>
       </c>
       <c r="C56" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>270</v>
+        <v>194</v>
       </c>
       <c r="F56" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G56" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H56" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B57" t="s">
-        <v>268</v>
+        <v>31</v>
       </c>
       <c r="C57" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="F57" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G57" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H57" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B58" t="s">
-        <v>262</v>
+        <v>318</v>
       </c>
       <c r="C58" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>328</v>
+        <v>194</v>
       </c>
       <c r="F58" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G58" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="H58" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B59" t="s">
-        <v>142</v>
+        <v>351</v>
       </c>
       <c r="C59" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="F59" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G59" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H59" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B60" t="s">
-        <v>142</v>
+        <v>318</v>
       </c>
       <c r="C60" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="F60" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="G60" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="H60" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
+        <v>312</v>
       </c>
       <c r="C61" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="F61" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="G61" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H61" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B62" t="s">
-        <v>142</v>
+        <v>318</v>
       </c>
       <c r="C62" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="F62" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G62" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H62" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B63" t="s">
-        <v>142</v>
+        <v>318</v>
       </c>
       <c r="C63" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>257</v>
+        <v>194</v>
       </c>
       <c r="F63" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G63" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H63" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B64" t="s">
-        <v>142</v>
+        <v>312</v>
       </c>
       <c r="C64" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>200</v>
+        <v>378</v>
       </c>
       <c r="F64" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="G64" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="H64" t="s">
-        <v>376</v>
+        <v>381</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>382</v>
+      </c>
+      <c r="B65" t="s">
+        <v>318</v>
+      </c>
+      <c r="C65" t="s">
+        <v>383</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>320</v>
+      </c>
+      <c r="F65" t="s">
+        <v>384</v>
+      </c>
+      <c r="G65" t="s">
+        <v>385</v>
+      </c>
+      <c r="H65" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>387</v>
+      </c>
+      <c r="B66" t="s">
+        <v>318</v>
+      </c>
+      <c r="C66" t="s">
+        <v>388</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>194</v>
+      </c>
+      <c r="F66" t="s">
+        <v>389</v>
+      </c>
+      <c r="G66" t="s">
+        <v>390</v>
+      </c>
+      <c r="H66" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>392</v>
+      </c>
+      <c r="B67" t="s">
+        <v>312</v>
+      </c>
+      <c r="C67" t="s">
+        <v>393</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" t="s">
+        <v>378</v>
+      </c>
+      <c r="F67" t="s">
+        <v>394</v>
+      </c>
+      <c r="G67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H67" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>397</v>
+      </c>
+      <c r="B68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" t="s">
+        <v>398</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>250</v>
+      </c>
+      <c r="F68" t="s">
+        <v>399</v>
+      </c>
+      <c r="G68" t="s">
+        <v>400</v>
+      </c>
+      <c r="H68" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>402</v>
+      </c>
+      <c r="B69" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" t="s">
+        <v>403</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>250</v>
+      </c>
+      <c r="F69" t="s">
+        <v>404</v>
+      </c>
+      <c r="G69" t="s">
+        <v>405</v>
+      </c>
+      <c r="H69" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>407</v>
+      </c>
+      <c r="B70" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" t="s">
+        <v>408</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" t="s">
+        <v>250</v>
+      </c>
+      <c r="F70" t="s">
+        <v>409</v>
+      </c>
+      <c r="G70" t="s">
+        <v>410</v>
+      </c>
+      <c r="H70" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>412</v>
+      </c>
+      <c r="B71" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" t="s">
+        <v>413</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>250</v>
+      </c>
+      <c r="F71" t="s">
+        <v>414</v>
+      </c>
+      <c r="G71" t="s">
+        <v>415</v>
+      </c>
+      <c r="H71" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>417</v>
+      </c>
+      <c r="B72" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" t="s">
+        <v>418</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>307</v>
+      </c>
+      <c r="F72" t="s">
+        <v>419</v>
+      </c>
+      <c r="G72" t="s">
+        <v>420</v>
+      </c>
+      <c r="H72" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>422</v>
+      </c>
+      <c r="B73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" t="s">
+        <v>423</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s">
+        <v>250</v>
+      </c>
+      <c r="F73" t="s">
+        <v>424</v>
+      </c>
+      <c r="G73" t="s">
+        <v>425</v>
+      </c>
+      <c r="H73" t="s">
+        <v>426</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-learn-about-medicare.report.xlsx
+++ b/tools/importer/reports/import-learn-about-medicare.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="442">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>employer-landing</t>
   </si>
   <si>
-    <t>2026-09-30T17:51:29.928Z</t>
+    <t>2026-09-30T20:30:12.433Z</t>
   </si>
   <si>
     <t>Boost Employee Health and Save Money with Highmark Employer Plans</t>
@@ -73,7 +73,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-30T16:04:26.807Z</t>
+    <t>2026-09-30T20:31:14.558Z</t>
   </si>
   <si>
     <t>Highmark: Health Insurance Plans for Individuals &amp; Businesses</t>
@@ -115,7 +115,7 @@
     <t>about-article</t>
   </si>
   <si>
-    <t>2026-09-30T18:08:29.686Z</t>
+    <t>2026-09-30T20:28:33.995Z</t>
   </si>
   <si>
     <t>Corporate Responsibility | Highmark</t>
@@ -130,7 +130,7 @@
     <t>about/our-story</t>
   </si>
   <si>
-    <t>2026-09-30T18:08:10.569Z</t>
+    <t>2026-09-30T20:28:14.133Z</t>
   </si>
   <si>
     <t>Highmark: Our Story</t>
@@ -151,7 +151,7 @@
     <t>employer-subpage</t>
   </si>
   <si>
-    <t>2026-09-30T17:19:36.476Z</t>
+    <t>2026-09-30T20:30:26.111Z</t>
   </si>
   <si>
     <t>Highmark Offers Employee Health Care Management Solutions</t>
@@ -169,7 +169,7 @@
     <t>employer/client-resources</t>
   </si>
   <si>
-    <t>2026-09-30T17:19:42.300Z</t>
+    <t>2026-09-30T20:30:31.175Z</t>
   </si>
   <si>
     <t>Client Resources for Highmark Employer Health Plans</t>
@@ -187,7 +187,7 @@
     <t>employer/cost-management</t>
   </si>
   <si>
-    <t>2026-09-30T17:19:29.603Z</t>
+    <t>2026-09-30T20:30:20.264Z</t>
   </si>
   <si>
     <t>Protect Your Self-Funded Health Care with Stop Loss Coverage.</t>
@@ -205,7 +205,7 @@
     <t>employer/solutions</t>
   </si>
   <si>
-    <t>2026-09-30T17:19:47.754Z</t>
+    <t>2026-09-30T20:30:36.600Z</t>
   </si>
   <si>
     <t>Highmark Business Solutions: Find the Right Plan for You</t>
@@ -223,7 +223,7 @@
     <t>employer/thought-leadership</t>
   </si>
   <si>
-    <t>2026-09-30T17:19:52.087Z</t>
+    <t>2026-09-30T20:30:42.221Z</t>
   </si>
   <si>
     <t>Thought Leadership Articles and Information | Highmark</t>
@@ -232,6 +232,48 @@
     <t>https://www.highmark.com/employer/thought-leadership?zg=false</t>
   </si>
   <si>
+    <t>newsroom/media-relations-contacts.report.json</t>
+  </si>
+  <si>
+    <t>["cards-minimal-dark-list","cards-minimal-dark-list","cards-minimal-dark-list","cards-minimal-dark-list","cards-minimal-dark-list","cards-minimal-dark-list","cards-minimal-dark-list","cards-minimal-dark-list"]</t>
+  </si>
+  <si>
+    <t>newsroom/media-relations-contacts</t>
+  </si>
+  <si>
+    <t>media-contacts</t>
+  </si>
+  <si>
+    <t>2026-09-30T20:27:18.287Z</t>
+  </si>
+  <si>
+    <t>Media Relations Contacts</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/newsroom/media-relations-contacts?zg=false</t>
+  </si>
+  <si>
+    <t>newsroom/weekly-capitol-hill-report.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>newsroom/weekly-capitol-hill-report</t>
+  </si>
+  <si>
+    <t>capitol-hill-report</t>
+  </si>
+  <si>
+    <t>2026-09-30T20:29:19.469Z</t>
+  </si>
+  <si>
+    <t>Weekly Capitol Hill Report</t>
+  </si>
+  <si>
+    <t>https://www.highmark.com/newsroom/weekly-capitol-hill-report?zg=false</t>
+  </si>
+  <si>
     <t>plans/d-snp.report.json</t>
   </si>
   <si>
@@ -361,7 +403,7 @@
     <t>chip-landing</t>
   </si>
   <si>
-    <t>2026-09-30T16:04:45.466Z</t>
+    <t>2026-09-30T20:29:28.745Z</t>
   </si>
   <si>
     <t>CHIP - Highmark Healthy Kids | Highmark Blue Cross Blue Shield</t>
@@ -382,7 +424,7 @@
     <t>bright-blue-futures</t>
   </si>
   <si>
-    <t>2026-09-30T18:19:49.316Z</t>
+    <t>2026-09-30T20:29:10.026Z</t>
   </si>
   <si>
     <t>Highmark Bright Blue Futures | Corporate Giving</t>
@@ -397,7 +439,7 @@
     <t>about/corporate-responsibility/social-determinants-of-health</t>
   </si>
   <si>
-    <t>2026-09-30T18:08:41.043Z</t>
+    <t>2026-09-30T20:28:44.847Z</t>
   </si>
   <si>
     <t>Social Determinants of Health (SDoH)</t>
@@ -412,7 +454,7 @@
     <t>about/corporate-responsibility/sustainability</t>
   </si>
   <si>
-    <t>2026-09-30T18:08:46.681Z</t>
+    <t>2026-09-30T20:28:51.099Z</t>
   </si>
   <si>
     <t>Highmark Sustainability: Our Commitment to a Healthier Future</t>
@@ -427,7 +469,7 @@
     <t>about/corporate-responsibility/valuing-our-people</t>
   </si>
   <si>
-    <t>2026-09-30T18:08:34.679Z</t>
+    <t>2026-09-30T20:28:39.250Z</t>
   </si>
   <si>
     <t>Highmark Health: Valuing Our People</t>
@@ -448,7 +490,7 @@
     <t>leadership</t>
   </si>
   <si>
-    <t>2026-09-30T18:12:42.349Z</t>
+    <t>2026-09-30T20:31:22.630Z</t>
   </si>
   <si>
     <t/>
@@ -463,7 +505,7 @@
     <t>about/our-story/mission-vision</t>
   </si>
   <si>
-    <t>2026-09-30T18:08:16.965Z</t>
+    <t>2026-09-30T20:28:20.313Z</t>
   </si>
   <si>
     <t>Mission, Vision, &amp; Core Behaviors</t>
@@ -478,7 +520,7 @@
     <t>about/our-story/our-businesses</t>
   </si>
   <si>
-    <t>2026-09-30T18:08:23.116Z</t>
+    <t>2026-09-30T20:28:27.216Z</t>
   </si>
   <si>
     <t>Highmark Health: Our Diverse Businesses and Affiliates</t>
@@ -499,7 +541,7 @@
     <t>find-care</t>
   </si>
   <si>
-    <t>2026-09-30T17:20:46.063Z</t>
+    <t>2026-09-30T20:30:50.778Z</t>
   </si>
   <si>
     <t>Find Care - Find a Provider | Highmark</t>
@@ -520,7 +562,7 @@
     <t>get-help</t>
   </si>
   <si>
-    <t>2026-09-30T18:20:20.581Z</t>
+    <t>2026-09-30T20:31:05.260Z</t>
   </si>
   <si>
     <t>Get Help Choosing a ACA Plan | Highmark ACA Specialists</t>
@@ -541,7 +583,7 @@
     <t>blue-neighbors</t>
   </si>
   <si>
-    <t>2026-09-30T17:20:37.848Z</t>
+    <t>2026-09-30T20:29:01.782Z</t>
   </si>
   <si>
     <t>Blue Neighbors - Volunteers for Seniors | Highmark</t>
@@ -559,7 +601,7 @@
     <t>plans/medicare/get-help</t>
   </si>
   <si>
-    <t>2026-09-30T18:20:14.588Z</t>
+    <t>2026-09-30T20:30:59.774Z</t>
   </si>
   <si>
     <t>Get Help Choosing a Medicare Plan | Highmark Medicare Specialists</t>
@@ -580,7 +622,7 @@
     <t>learn-about-medicare</t>
   </si>
   <si>
-    <t>2026-09-30T18:20:29.993Z</t>
+    <t>2026-09-30T20:31:33.938Z</t>
   </si>
   <si>
     <t>Learn About Medicare | Highmark</t>
@@ -598,7 +640,7 @@
     <t>sidebar-listing</t>
   </si>
   <si>
-    <t>2026-08-17T21:42:16.291Z</t>
+    <t>2026-09-30T19:00:22.830Z</t>
   </si>
   <si>
     <t>Health Insurance Articles | Highmark</t>
@@ -613,7 +655,7 @@
     <t>resources/answers/community-assistance-resources</t>
   </si>
   <si>
-    <t>2026-08-17T21:42:20.566Z</t>
+    <t>2026-09-30T19:00:28.526Z</t>
   </si>
   <si>
     <t>Community Assistance Resources| Highmark</t>
@@ -631,7 +673,7 @@
     <t>resources/answers/faq</t>
   </si>
   <si>
-    <t>2026-08-17T21:42:25.130Z</t>
+    <t>2026-09-30T19:00:35.343Z</t>
   </si>
   <si>
     <t>Highmark FAQ: Answers to Your Health Questions</t>
@@ -766,7 +808,7 @@
     <t>sidebar-guide-article</t>
   </si>
   <si>
-    <t>2026-08-18T00:53:55.514Z</t>
+    <t>2026-09-30T19:02:53.853Z</t>
   </si>
   <si>
     <t>What Causes Mental Health Problems | Highmark</t>
@@ -853,7 +895,7 @@
     <t>chip</t>
   </si>
   <si>
-    <t>2026-09-30T13:22:01.251Z</t>
+    <t>2026-09-30T20:29:37.300Z</t>
   </si>
   <si>
     <t>CHIP Eligibility and Costs | Highmark Blue Cross Blue Shield</t>
@@ -871,7 +913,7 @@
     <t>western-pennsylvania/chip/chip-enhanced-member-supports-and-case-management</t>
   </si>
   <si>
-    <t>2026-09-30T13:22:24.246Z</t>
+    <t>2026-09-30T20:30:03.563Z</t>
   </si>
   <si>
     <t>CHIP Enhanced Member Supports and Case Management | Highmark Blue Cross Blue Shield</t>
@@ -886,7 +928,7 @@
     <t>western-pennsylvania/chip/chip-resources</t>
   </si>
   <si>
-    <t>2026-09-30T13:22:05.883Z</t>
+    <t>2026-09-30T20:29:42.811Z</t>
   </si>
   <si>
     <t>CHIP Resources | Highmark Blue Cross Blue Shield</t>
@@ -901,7 +943,7 @@
     <t>western-pennsylvania/chip/doctors-drugs</t>
   </si>
   <si>
-    <t>2026-09-30T13:22:11.986Z</t>
+    <t>2026-09-30T20:29:49.022Z</t>
   </si>
   <si>
     <t>CHIP Doctors and Drugs | Highmark Blue Cross Blue Shield</t>
@@ -919,7 +961,7 @@
     <t>western-pennsylvania/chip/what-is-chip</t>
   </si>
   <si>
-    <t>2026-09-30T13:22:17.711Z</t>
+    <t>2026-09-30T20:29:56.215Z</t>
   </si>
   <si>
     <t>What is CHIP? | Highmark Blue Cross Blue Shield</t>
@@ -937,7 +979,7 @@
     <t>sidebar-article</t>
   </si>
   <si>
-    <t>2026-08-17T23:32:30.506Z</t>
+    <t>2026-09-30T19:01:41.551Z</t>
   </si>
   <si>
     <t>Learn the Benefits of Using Health Spending Accounts | Highmark</t>
@@ -955,7 +997,7 @@
     <t>resources/answers/faq/aca-plans</t>
   </si>
   <si>
-    <t>2026-08-17T21:42:29.889Z</t>
+    <t>2026-09-30T19:00:41.076Z</t>
   </si>
   <si>
     <t>Frequently Asked ACA Questions | Highmark</t>
@@ -976,7 +1018,7 @@
     <t>sidebar-faq</t>
   </si>
   <si>
-    <t>2026-08-17T23:22:34.461Z</t>
+    <t>2026-09-30T19:01:54.931Z</t>
   </si>
   <si>
     <t>Mental and Behavioral Health Medications FAQ</t>
@@ -991,7 +1033,7 @@
     <t>resources/answers/faq/chip</t>
   </si>
   <si>
-    <t>2026-08-17T21:42:33.991Z</t>
+    <t>2026-09-30T19:00:45.421Z</t>
   </si>
   <si>
     <t>Frequently Asked CHIP Questions | Highmark</t>
@@ -1009,7 +1051,7 @@
     <t>resources/answers/faq/covid</t>
   </si>
   <si>
-    <t>2026-08-17T21:42:38.973Z</t>
+    <t>2026-09-30T19:00:49.676Z</t>
   </si>
   <si>
     <t>Frequently Asked COVID Questions | Highmark</t>
@@ -1024,7 +1066,7 @@
     <t>resources/answers/faq/ebill-help</t>
   </si>
   <si>
-    <t>2026-08-17T21:42:43.621Z</t>
+    <t>2026-09-30T19:00:54.819Z</t>
   </si>
   <si>
     <t>Highmark eBill Help FAQ | Highmark</t>
@@ -1039,7 +1081,7 @@
     <t>resources/answers/faq/ebill-terms</t>
   </si>
   <si>
-    <t>2026-08-17T21:42:49.603Z</t>
+    <t>2026-09-30T19:00:59.986Z</t>
   </si>
   <si>
     <t>Highmark eBill Terms of Use | Highmark</t>
@@ -1054,7 +1096,7 @@
     <t>resources/answers/faq/explanation-of-benefits</t>
   </si>
   <si>
-    <t>2026-08-17T21:42:54.303Z</t>
+    <t>2026-09-30T19:01:06.522Z</t>
   </si>
   <si>
     <t>Explanation of Benefits FAQ | Highmark</t>
@@ -1072,7 +1114,7 @@
     <t>resources/answers/faq/home-prescription-delivery</t>
   </si>
   <si>
-    <t>2026-08-17T23:22:39.695Z</t>
+    <t>2026-09-30T19:02:00.776Z</t>
   </si>
   <si>
     <t>Home Prescription Delivery &amp; DME FAQ</t>
@@ -1087,7 +1129,7 @@
     <t>resources/answers/faq/insurance-terms</t>
   </si>
   <si>
-    <t>2026-08-17T21:43:00.279Z</t>
+    <t>2026-09-30T19:01:11.475Z</t>
   </si>
   <si>
     <t>Definitions of Common Insurance Terms</t>
@@ -1102,7 +1144,7 @@
     <t>resources/answers/faq/measles</t>
   </si>
   <si>
-    <t>2026-08-17T21:43:04.730Z</t>
+    <t>2026-09-30T19:01:16.783Z</t>
   </si>
   <si>
     <t>Measles FAQ: Symptoms, Prevention, Risks and Resources</t>
@@ -1114,13 +1156,16 @@
     <t>resources/answers/faq/medicare-reservations.report.json</t>
   </si>
   <si>
+    <t>["cards-minimal-light-sidenav","cards-minimal-light-sidenav","accordion-minimal-light","accordion-minimal-light","accordion-minimal-light","accordion-minimal-light","accordion-minimal-light","accordion-minimal-light"]</t>
+  </si>
+  <si>
     <t>resources/answers/faq/medicare-reservations</t>
   </si>
   <si>
-    <t>2026-08-17T21:43:09.024Z</t>
-  </si>
-  <si>
-    <t>All About Medicare Reservations - Connect with an Advisor Near You</t>
+    <t>2026-09-30T19:01:22.054Z</t>
+  </si>
+  <si>
+    <t>Medicare Advantage FAQs: Common Questions | Highmark</t>
   </si>
   <si>
     <t>https://www.highmark.com/resources/answers/faq/medicare-reservations</t>
@@ -1132,7 +1177,7 @@
     <t>resources/answers/faq/member-account-login</t>
   </si>
   <si>
-    <t>2026-08-17T21:43:15.365Z</t>
+    <t>2026-09-30T19:01:27.250Z</t>
   </si>
   <si>
     <t>Member Account Login FAQ | Highmark</t>
@@ -1150,7 +1195,7 @@
     <t>sidebar-grouped-faq</t>
   </si>
   <si>
-    <t>2026-08-18T00:34:45.235Z</t>
+    <t>2026-09-30T19:02:13.789Z</t>
   </si>
   <si>
     <t>Blue Fund Grants FAQ for Northeastern New York Nonprofits</t>
@@ -1165,7 +1210,7 @@
     <t>resources/answers/faq/preventive-diagnostic-screening</t>
   </si>
   <si>
-    <t>2026-08-17T23:22:45.618Z</t>
+    <t>2026-09-30T19:02:06.551Z</t>
   </si>
   <si>
     <t>Preventive Screening vs. Diagnostic | Highmark</t>
@@ -1180,7 +1225,7 @@
     <t>resources/answers/faq/spending-accounts</t>
   </si>
   <si>
-    <t>2026-08-17T21:43:19.937Z</t>
+    <t>2026-09-30T19:01:33.083Z</t>
   </si>
   <si>
     <t>Spending Accounts FAQ: FSA, HAS, HRA | Highmark</t>
@@ -1195,7 +1240,7 @@
     <t>resources/answers/faq/western-ny-blue-fund</t>
   </si>
   <si>
-    <t>2026-08-18T00:34:50.945Z</t>
+    <t>2026-09-30T19:02:20.134Z</t>
   </si>
   <si>
     <t>Blue Fund Grants FAQ for Western New York Nonprofits</t>
@@ -1210,7 +1255,7 @@
     <t>resources/mental-health-services/anxiety/treatments</t>
   </si>
   <si>
-    <t>2026-08-18T00:53:25.601Z</t>
+    <t>2026-09-30T19:02:28.175Z</t>
   </si>
   <si>
     <t>Anxiety Counseling, Medication, Life Changes| Highmark</t>
@@ -1225,7 +1270,7 @@
     <t>resources/mental-health-services/anxiety/warning-signs</t>
   </si>
   <si>
-    <t>2026-08-18T00:53:32.288Z</t>
+    <t>2026-09-30T19:02:33.637Z</t>
   </si>
   <si>
     <t>Anxiety Warning Signs and Types of Anxiety | Highmark</t>
@@ -1240,7 +1285,7 @@
     <t>resources/mental-health-services/depression/depression-types</t>
   </si>
   <si>
-    <t>2026-08-18T00:53:38.295Z</t>
+    <t>2026-09-30T19:02:38.789Z</t>
   </si>
   <si>
     <t>Different Types of Depression| Highmark</t>
@@ -1255,7 +1300,7 @@
     <t>resources/mental-health-services/depression/help-someone-with-depression</t>
   </si>
   <si>
-    <t>2026-08-18T00:53:43.853Z</t>
+    <t>2026-09-30T19:02:43.189Z</t>
   </si>
   <si>
     <t>How to Help Someone With Depression | Highmark</t>
@@ -1270,7 +1315,7 @@
     <t>resources/mental-health-services/eating-disorders/eating-disorder-types</t>
   </si>
   <si>
-    <t>2026-08-18T00:51:56.883Z</t>
+    <t>2026-09-30T19:01:47.684Z</t>
   </si>
   <si>
     <t>Different Types of Eating Disorders | Highmark</t>
@@ -1285,7 +1330,7 @@
     <t>resources/mental-health-services/eating-disorders/help-someone-with-eating-disorder</t>
   </si>
   <si>
-    <t>2026-08-18T00:53:49.250Z</t>
+    <t>2026-09-30T19:02:49.312Z</t>
   </si>
   <si>
     <t>How to Help Someone With an Eating Disorder | Highmark</t>
@@ -1680,7 +1725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -2032,120 +2077,120 @@
         <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="F18" t="s">
         <v>116</v>
@@ -2188,62 +2233,62 @@
         <v>126</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="F20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G20" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="F21" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G21" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H21" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -2252,50 +2297,50 @@
         <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H22" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>144</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G23" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H23" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -2304,82 +2349,82 @@
         <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G24" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H24" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>158</v>
       </c>
       <c r="F25" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G25" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>168</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
         <v>169</v>
@@ -2431,1160 +2476,1212 @@
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="F29" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G29" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C30" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F30" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G30" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H30" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>194</v>
       </c>
       <c r="C31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="F31" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G31" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H31" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="C32" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="F32" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G32" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H32" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B33" t="s">
-        <v>204</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F33" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G33" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H33" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B34" t="s">
-        <v>210</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>95</v>
+        <v>208</v>
       </c>
       <c r="F34" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G34" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H34" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B35" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C35" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>108</v>
+        <v>208</v>
       </c>
       <c r="F35" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G35" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H35" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B36" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C36" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F36" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G36" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H36" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B37" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C37" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="F37" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G37" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H37" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B38" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C38" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="F38" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G38" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H38" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B39" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C39" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="F39" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H39" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B40" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="C40" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="F40" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G40" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H40" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>252</v>
       </c>
       <c r="C41" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>250</v>
+        <v>122</v>
       </c>
       <c r="F41" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G41" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H41" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B42" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="C42" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="F42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G42" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B43" t="s">
-        <v>261</v>
+        <v>31</v>
       </c>
       <c r="C43" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>95</v>
+        <v>264</v>
       </c>
       <c r="F43" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G43" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H43" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B44" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="C44" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F44" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G44" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H44" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B45" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="C45" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F45" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G45" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H45" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B46" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C46" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="F46" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G46" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H46" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B47" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C47" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="F47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G47" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H47" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B48" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C48" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="F48" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G48" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H48" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B49" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C49" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="F49" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G49" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="H49" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B50" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C50" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="F50" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G50" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H50" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>298</v>
       </c>
       <c r="C51" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="F51" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G51" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B52" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C52" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>194</v>
+        <v>293</v>
       </c>
       <c r="F52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H52" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B53" t="s">
-        <v>318</v>
+        <v>31</v>
       </c>
       <c r="C53" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
       </c>
       <c r="E53" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F53" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G53" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H53" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B54" t="s">
-        <v>204</v>
+        <v>326</v>
       </c>
       <c r="C54" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F54" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G54" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H54" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B55" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C55" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>194</v>
+        <v>334</v>
       </c>
       <c r="F55" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G55" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H55" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s">
-        <v>312</v>
+        <v>218</v>
       </c>
       <c r="C56" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F56" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G56" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H56" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>344</v>
       </c>
       <c r="C57" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F57" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G57" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="H57" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B58" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C58" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F58" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G58" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H58" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B59" t="s">
-        <v>351</v>
+        <v>31</v>
       </c>
       <c r="C59" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>320</v>
+        <v>208</v>
       </c>
       <c r="F59" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="G59" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H59" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B60" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C60" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F60" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G60" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H60" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B61" t="s">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="C61" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>194</v>
+        <v>334</v>
       </c>
       <c r="F61" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="G61" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H61" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B62" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C62" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F62" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G62" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="H62" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B63" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C63" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F63" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G63" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H63" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B64" t="s">
-        <v>312</v>
+        <v>381</v>
       </c>
       <c r="C64" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>378</v>
+        <v>208</v>
       </c>
       <c r="F64" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="G64" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H64" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B65" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C65" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>320</v>
+        <v>208</v>
       </c>
       <c r="F65" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="G65" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H65" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B66" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C66" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
       </c>
       <c r="E66" t="s">
-        <v>194</v>
+        <v>393</v>
       </c>
       <c r="F66" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G66" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="H66" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B67" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="C67" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>378</v>
+        <v>334</v>
       </c>
       <c r="F67" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="G67" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="H67" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>332</v>
       </c>
       <c r="C68" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
       </c>
       <c r="E68" t="s">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="F68" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="G68" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="H68" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>326</v>
       </c>
       <c r="C69" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
       </c>
       <c r="E69" t="s">
-        <v>250</v>
+        <v>393</v>
       </c>
       <c r="F69" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="G69" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H69" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B70" t="s">
         <v>31</v>
       </c>
       <c r="C70" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
       </c>
       <c r="E70" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="F70" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="G70" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H70" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B71" t="s">
         <v>31</v>
       </c>
       <c r="C71" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
       </c>
       <c r="E71" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="F71" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="G71" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="H71" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B72" t="s">
         <v>31</v>
       </c>
       <c r="C72" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
       </c>
       <c r="E72" t="s">
-        <v>307</v>
+        <v>264</v>
       </c>
       <c r="F72" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="G72" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="H72" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s">
         <v>31</v>
       </c>
       <c r="C73" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
       </c>
       <c r="E73" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="F73" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="G73" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H73" t="s">
-        <v>426</v>
+        <v>431</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>432</v>
+      </c>
+      <c r="B74" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" t="s">
+        <v>433</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" t="s">
+        <v>321</v>
+      </c>
+      <c r="F74" t="s">
+        <v>434</v>
+      </c>
+      <c r="G74" t="s">
+        <v>435</v>
+      </c>
+      <c r="H74" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>437</v>
+      </c>
+      <c r="B75" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" t="s">
+        <v>438</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" t="s">
+        <v>264</v>
+      </c>
+      <c r="F75" t="s">
+        <v>439</v>
+      </c>
+      <c r="G75" t="s">
+        <v>440</v>
+      </c>
+      <c r="H75" t="s">
+        <v>441</v>
       </c>
     </row>
   </sheetData>
